--- a/docs/security/MaxAlgos_VAPT_Scoping_Questionnaire.xlsx
+++ b/docs/security/MaxAlgos_VAPT_Scoping_Questionnaire.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,9 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="001F3864"/>
     </font>
     <font>
       <i val="1"/>
@@ -105,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -128,6 +131,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -630,19 +636,19 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>OS Version</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Ubuntu 22.04 LTS (host)</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Docker Compose containerized deployment (docker-compose.prod.yml). We'll confirm the exact base image/package versions inside the application container itself if you need that level of detail.</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04 LTS (host) — Debian 11 (Bullseye) inside the app container, Python 3.12.11</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Docker Compose containerized deployment (docker-compose.prod.yml). Host OS is Ubuntu 22.04 LTS; the maxalgos:latest application container itself runs on Debian 11 Bullseye (confirmed via /etc/os-release) with Python 3.12.11.</t>
         </is>
       </c>
     </row>
@@ -762,19 +768,19 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Estimated Testing Time</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>5–7 business days</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>We'll confirm exact start/end calendar dates with you before kickoff.</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Exact calendar start/end dates to be fixed jointly with the auditor at engagement kickoff, once duration is agreed.</t>
         </is>
       </c>
     </row>
@@ -803,12 +809,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Nginx (reverse proxy) + Gunicorn with eventlet worker class (-w 1, single worker — required for our WebSocket/SocketIO architecture).</t>
+          <t>Nginx 1.24.0 (Ubuntu) reverse proxy + Gunicorn with eventlet worker class (-w 1, single worker — required for our WebSocket/SocketIO architecture).</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Nginx is the only reverse proxy in front of the application — no CDN or additional proxy layer. We'll confirm the exact nginx version installed on the server if you need it for version-specific CVE checks.</t>
+          <t>Nginx is installed directly on the Ubuntu host (not containerized) and is the only reverse proxy in front of the application — no CDN or additional proxy layer. Version confirmed via `nginx -v` on the production server.</t>
         </is>
       </c>
     </row>
@@ -919,7 +925,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Unified market-data WebSocket proxy, separate from SocketIO — we'll confirm the exact external exposure with you before testing</t>
+          <t>Unified market-data WebSocket proxy, separate from SocketIO. Confirmed externally exposed: docker-compose.prod.yml publishes 0.0.0.0:8765-&gt;8785/tcp on the production host.</t>
         </is>
       </c>
     </row>
@@ -945,7 +951,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>These are the 28 brokers we actually ship as implemented plugins (each with a plugin.json, auth/order/data modules, and symbol mapping) — see the 'Third-Party Dependencies' sheet for each one's real API domain. We'll confirm which of these are actively used by live customer accounts in production so you can prioritize.</t>
+          <t>These are the 28 brokers we actually ship as implemented plugins (each with a plugin.json, auth/order/data modules, and symbol mapping) — see the 'Third-Party Dependencies' sheet for each one's real API domain. Confirmed on the production database: 4 brokers currently have live user-linked credentials — sharekhan, bnr, aliceblue, and zebu. These 4 should be prioritized for OAuth/credential-flow testing; the remaining 24 plugins are available to any user but have no active connections at present.</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1271,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Confirmed on the production server: we run 6 separate SQLite databases — maxalgos.db (main), logs.db (traffic/API logs), latency.db (latency monitoring), health.db (health monitoring), sandbox.db (sandbox trading), and historify.duckdb (historical market data, DuckDB). Our docker-compose file also provisions a Postgres 16 container, but production's actual DATABASE_URL and related env vars are still set to the sqlite:/// defaults, so Postgres is not in active use.</t>
+          <t>Mixed backend, confirmed on the production server: our main database (DATABASE_URL — users, auth, orders, strategies, payments, sessions, and most other application tables) now runs on PostgreSQL 16, migrated from SQLite. Five other databases remain on SQLite by design: logs.db (traffic/API logs), latency.db (latency monitoring), health.db (health monitoring), sandbox.db (sandbox trading), and a dedicated SYMBOL_DATABASE_URL override that keeps the large, frequently-refreshed symbol/master-contract table (symtoken) on SQLite even though it logically belongs to the main database. historify.duckdb (historical market data) is DuckDB and unaffected by this change. Postgres runs in its own Docker container on the same VPS, reachable only from the app container over the internal Docker network (not exposed on any host port).</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -3311,7 +3317,7 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>We'll confirm before kickoff which of these 28 brokers currently hold live customer credentials in production, so you can prioritize the ones with real attack surface first.</t>
+          <t>Confirmed on the production database: 4 of these 28 brokers currently hold live customer credentials — sharekhan, bnr, aliceblue, and zebu. Prioritize these for OAuth/credential-flow testing; the remaining 24 are supported but have no active user connections at present.</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3436,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SQLite (active) — file-based, not network-exposed. Postgres 16 container is provisioned but not in use (not exposed on any host port either way)</t>
+          <t>Mixed: Postgres 16 (main database — users, orders, strategies, payments) + SQLite (logs, latency, health, sandbox, symbol/master-contract table). Neither is exposed on any host port.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Confirmed on the production server: DATABASE_URL and related env vars point to sqlite:/// files under db/</t>
+          <t>Postgres reachable only from the app container over the internal Docker network (hostname 'postgres', port 5432 not published to the host). SQLite files are local to the app container's filesystem, not network-accessible at all.</t>
         </is>
       </c>
     </row>
@@ -3447,12 +3453,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Nginx</t>
+          <t>Nginx 1.24.0 (Ubuntu), installed directly on the host (not containerized)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Nginx is the only reverse proxy in front of the application — no CDN or additional proxy layer. We'll confirm exact version if needed for CVE checks.</t>
+          <t>The only reverse proxy in front of the application — no CDN or additional proxy layer. Version confirmed via `nginx -v` on the production server.</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3504,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>To be confirmed with SPOC — see 'Testing Access' sheet</t>
+          <t>Not granted by default for this engagement</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>We'll confirm whether SSH/console-level access is granted for this engagement or if infra testing is external/network-layer only</t>
+          <t>Infrastructure testing is external/network-layer only for this cycle; OS/patch-level detail is self-attested above. If the CERT-In auditor's methodology requires config-level verification to satisfy SEBI circular SEBI/HO/ITD-1/ITD_CSC_EXT/P/CIR/2024/113, a time-boxed read-only SSH account (key-based, bastion-restricted, auto-expiring) can be provisioned on request.</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3521,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Managed at VPS level (not in application codebase)</t>
+          <t>No host-level firewall (ufw inactive, iptables INPUT policy is ACCEPT with no filtering rules). Exposure is controlled entirely by Docker's own auto-managed iptables rules.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>We'll confirm current firewall rules (allowed inbound ports, source restrictions) with our infra owner before testing</t>
+          <t>Confirmed via `sudo ufw status verbose` (inactive) and `iptables -L -n` on the production server: only the container's published ports (5000→8090, 8785→8765) are reachable, enforced by Docker's DOCKER chain, not a separate host firewall.</t>
         </is>
       </c>
     </row>
@@ -3532,17 +3538,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>To be confirmed with SPOC</t>
+          <t>No automated backup/snapshot policy currently in place</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Relevant for infra resilience checks and post-engagement rollback if needed</t>
+          <t>The only existing backup is a manual db.bak.&lt;date&gt;/ folder created during our recent database migration — not a recurring or automated process</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Infrastructure testing is included in this engagement per SEBI circular SEBI/HO/ITD-1/ITD_CSC_EXT/P/CIR/2024/113 (20 Aug 2024), which requires half-yearly VAPT covering Application, APIs, and Infrastructure together, performed by a CERT-In empanelled auditor.</t>
         </is>
@@ -3590,7 +3596,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Vault Reference (fill with real pointer, never plaintext)</t>
+          <t>Hand-off Method (not shared in this document)</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -3617,7 +3623,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>&lt;&lt; enter real vault path/pointer here &gt;&gt;</t>
+          <t>Shared directly with the auditor via email or WhatsApp to the SPOC at kickoff — never written in this document</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -3644,7 +3650,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>&lt;&lt; enter real vault path/pointer here &gt;&gt;</t>
+          <t>Shared directly with the auditor via email or WhatsApp to the SPOC at kickoff — never written in this document</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -3671,7 +3677,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>&lt;&lt; enter real vault path/pointer here &gt;&gt;</t>
+          <t>Shared directly with the auditor via email or WhatsApp to the SPOC at kickoff — never written in this document</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3683,7 +3689,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Production server SSH/console access (if in scope)</t>
+          <t>Production server SSH/console access</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3698,19 +3704,19 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>&lt;&lt; enter real vault path/pointer here, or N/A if out of scope &gt;&gt;</t>
+          <t>N/A — not granted by default for this engagement</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>We'll confirm whether infra-level (server/OS) access is in scope, or web/API-layer only</t>
+          <t>External/network-layer testing only for this cycle. A time-boxed, read-only, key-based, bastion-restricted, auto-expiring SSH account can be provisioned on request if the auditor's methodology requires config-level verification (see 'Infrastructure Scope' sheet)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>We'll populate the Vault Reference column with our actual secrets-manager pointer (1Password item, Bitwarden share, HashiCorp Vault path, etc.) before kickoff. We will not send plaintext credentials in this spreadsheet.</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>User credentials, admin credentials, and sandbox broker API keys are shared directly with the auditor's team by email or WhatsApp to our SPOC (M. Ganeshamoorthy) at the start of the engagement — they are never written into this scoping document in plaintext or otherwise.</t>
         </is>
       </c>
     </row>
